--- a/data/routes_03012026.xlsx
+++ b/data/routes_03012026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rf50/playground/amtrak-map/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rf50/playground/amtrak-map/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{912626D0-B5F2-F44E-9E11-B09A8494C79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9AA750A-0B6F-A846-9B4D-147F42F0F514}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8080" yWindow="600" windowWidth="20720" windowHeight="16660" xr2:uid="{22AC9FD6-AE6E-7D4C-946C-D1D228A595B3}"/>
   </bookViews>
@@ -147,7 +147,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="309">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="310">
   <si>
     <t>route</t>
   </si>
@@ -1074,6 +1074,9 @@
   </si>
   <si>
     <t>#9830A0</t>
+  </si>
+  <si>
+    <t>no</t>
   </si>
 </sst>
 </file>
@@ -1185,37 +1188,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1822,6 +1795,9 @@
       <c r="K6">
         <v>410</v>
       </c>
+      <c r="L6" t="s">
+        <v>309</v>
+      </c>
       <c r="M6" t="s">
         <v>277</v>
       </c>
@@ -2558,7 +2534,7 @@
         <v>90</v>
       </c>
       <c r="L23" t="s">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="M23" t="s">
         <v>308</v>
